--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,145 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.45</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="C10" t="n">
         <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,146 +448,236 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.45</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="C10" t="n">
         <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
-      </c>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,96 +589,6 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,6 +589,86 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,151 +448,139 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>1.33</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.65</v>
-      </c>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -602,7 +590,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -612,7 +600,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -622,7 +610,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -632,7 +620,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -642,7 +630,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -652,7 +640,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -662,12 +650,22 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,201 +448,231 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="C4" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.05</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.71</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.78</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -652,7 +682,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -662,12 +692,34 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D5" t="n">
         <v>3.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +538,7 @@
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D10" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="C13" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="D13" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="14">

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,277 +448,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.3</v>
+        <v>2.55</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C6" t="n">
         <v>3.75</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.05</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,49 +448,213 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>9.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="C4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C5" t="n">
         <v>3.5</v>
       </c>
-      <c r="D4" t="n">
-        <v>3.75</v>
+      <c r="D5" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.09</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,14 +448,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
         <v>4.5</v>
@@ -464,197 +464,129 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="C4" t="n">
         <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.77</v>
+        <v>3.4</v>
       </c>
       <c r="C7" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="n">
-        <v>4.71</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="n">
-        <v>4.76</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="C9" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="C10" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
         <v>4.5</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="C4" t="n">
         <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         <v>3.75</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="C7" t="n">
         <v>3.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="C8" t="n">
         <v>3.2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="C10" t="n">
         <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,129 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="D5" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="C7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,128 +448,80 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D9" t="n">
         <v>1.8</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.38</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C6" t="n">
         <v>4.1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C10" t="n">
         <v>3.8</v>
       </c>
-      <c r="D6" t="n">
-        <v>1.8</v>
+      <c r="D10" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="C3" t="n">
         <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="4">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="C5" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="D5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="C6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,157 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="C10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D18" t="n">
         <v>3.8</v>
       </c>
-      <c r="D10" t="n">
-        <v>4.5</v>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,289 +448,81 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="C2" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="C4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MPiooIM</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="C5" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D9" t="n">
         <v>4.33</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>nTCJapXF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.6</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>1.8</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.75</v>
       </c>
-      <c r="D6" t="n">
-        <v>4.33</v>
+      <c r="D19" t="n">
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,110 +448,110 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.35</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.42</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="n">
         <v>3.2</v>
@@ -560,177 +560,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D10" t="n">
         <v>2.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="C4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D4" t="n">
         <v>3.9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="C5" t="n">
         <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>1.8</v>
       </c>
-      <c r="C6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
         <v>4.33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="C2" t="n">
         <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         <v>1.38</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="D3" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D5" t="n">
         <v>1.75</v>
@@ -519,10 +519,10 @@
         <v>1.33</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="C7" t="n">
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="8">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C8" t="n">
         <v>3.2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.3</v>
       </c>
       <c r="D8" t="n">
         <v>2.2</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="C9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
         <v>4.75</v>
@@ -583,154 +583,10 @@
         <v>3.4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,144 +448,64 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="C2" t="n">
         <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.38</v>
+        <v>3.5</v>
       </c>
       <c r="C3" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D10" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,46 +448,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.55</v>
+        <v>1.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
         <v>4.5</v>
@@ -496,17 +496,113 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,161 +448,225 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="C7" t="n">
         <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="D8" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.75</v>
+        <v>1.3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="C11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,226 +448,236 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="C2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2" t="n">
         <v>3.7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3</v>
+        <v>4.33</v>
       </c>
       <c r="C10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>8.5</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.2</v>
-      </c>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.8</v>
-      </c>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.5</v>
-      </c>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7</v>
-      </c>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.73</v>
-      </c>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C3" t="n">
         <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -506,7 +506,7 @@
         <v>5.5</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="C9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D9" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="10">
@@ -595,9 +595,15 @@
           <t>lYpTkOLs</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -605,9 +611,15 @@
           <t>p0vxl2jf</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -615,9 +627,15 @@
           <t>hQspntL6</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -625,9 +643,15 @@
           <t>vaZNtoqR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -635,9 +659,15 @@
           <t>WdE2Z2y1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -645,9 +675,15 @@
           <t>vNHAXt6D</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -655,9 +691,15 @@
           <t>KdJMr7EE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.35</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -665,9 +707,15 @@
           <t>h2acepbK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.85</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -675,9 +723,15 @@
           <t>AsQgyP6l</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>2.9</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="D3" t="n">
         <v>2.5</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="C5" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="D5" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C6" t="n">
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="C7" t="n">
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="C8" t="n">
         <v>3.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="C9" t="n">
         <v>3.75</v>
       </c>
       <c r="D9" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -727,10 +727,10 @@
         <v>3.45</v>
       </c>
       <c r="C19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,30 +448,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
         <v>2.5</v>
@@ -480,257 +480,49 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="C4" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="C5" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>KdJMr7EE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>3.1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C6" t="n">
         <v>4.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="C2" t="n">
         <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>3.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
         <v>2.2</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="C8" t="n">
         <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
@@ -580,156 +580,12 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C10" t="n">
         <v>3.6</v>
       </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="D10" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D19" t="n">
         <v>1.95</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>bqYbtBlo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>n5Eg2hB4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" t="n">
         <v>3.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="C8" t="n">
         <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="C9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
         <v>1.95</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nRkUEVfA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QB1LGiQc</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WWnG5RHd</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
         <v>6.5</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="C3" t="n">
         <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>6.25</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="D5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C8" t="n">
         <v>3.6</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -580,157 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="C10" t="n">
         <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
         <v>2.05</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,145 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
         <v>6.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="C3" t="n">
         <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
         <v>3.5</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
       <c r="D8" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -487,10 +487,10 @@
         <v>1.6</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="D5" t="n">
         <v>1.22</v>
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="C6" t="n">
         <v>3.2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="C8" t="n">
         <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="9">
@@ -587,6 +587,70 @@
       </c>
       <c r="D10" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
